--- a/examples/sales_to_billing.xlsx
+++ b/examples/sales_to_billing.xlsx
@@ -59,12 +59,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F7F9FC"/>
+        <fgColor rgb="00D4DFF0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4DFF0"/>
+        <fgColor rgb="00F7F9FC"/>
       </patternFill>
     </fill>
     <fill>
@@ -82,6 +82,20 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color rgb="00333333"/>
+      </left>
+      <right style="medium">
+        <color rgb="00333333"/>
+      </right>
+      <top style="medium">
+        <color rgb="00333333"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00333333"/>
+      </bottom>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="008A99B3"/>
       </left>
@@ -93,20 +107,6 @@
       </top>
       <bottom style="thin">
         <color rgb="008A99B3"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="00333333"/>
-      </left>
-      <right style="medium">
-        <color rgb="00333333"/>
-      </right>
-      <top style="medium">
-        <color rgb="00333333"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="00333333"/>
       </bottom>
     </border>
   </borders>
@@ -121,11 +121,11 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -206,16 +206,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>180975</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
+      <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
+      <xdr:colOff>619125</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
+      <xdr:rowOff>657225</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -224,7 +224,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="847725" y="1393825"/>
+          <a:off x="180975" y="1781175"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartTerminator">
@@ -259,16 +259,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>180975</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
+      <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
+      <xdr:colOff>619125</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
+      <xdr:rowOff>657225</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -277,7 +277,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="847725" y="2282825"/>
+          <a:off x="180975" y="2667000"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -312,16 +312,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>180975</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
+      <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
+      <xdr:colOff>619125</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
+      <xdr:rowOff>657225</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -330,7 +330,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="847725" y="3171825"/>
+          <a:off x="180975" y="3552825"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartDecision">
@@ -365,16 +365,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>981075</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
+      <xdr:colOff>619125</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
+      <xdr:rowOff>657225</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -383,7 +383,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2447925" y="4060825"/>
+          <a:off x="1781175" y="4438650"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -418,16 +418,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>981075</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
+      <xdr:colOff>619125</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
+      <xdr:rowOff>657225</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -436,7 +436,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4048125" y="4949825"/>
+          <a:off x="3381375" y="5324475"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -471,16 +471,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>981075</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
+      <xdr:colOff>619125</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
+      <xdr:rowOff>657225</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -489,7 +489,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4048125" y="5838825"/>
+          <a:off x="3381375" y="6210300"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartTerminator">
@@ -524,16 +524,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>800101</xdr:colOff>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>180976</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
+      <xdr:rowOff>219075</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -545,8 +545,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1466850" y="1831975"/>
-          <a:ext cx="1" cy="450850"/>
+          <a:off x="180975" y="1781175"/>
+          <a:ext cx="1" cy="885825"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -563,16 +563,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>800101</xdr:colOff>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>180976</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
+      <xdr:rowOff>219075</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -584,8 +584,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1466850" y="2720975"/>
-          <a:ext cx="1" cy="450850"/>
+          <a:off x="180975" y="2667000"/>
+          <a:ext cx="1" cy="885825"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -602,16 +602,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
+      <xdr:colOff>981075</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
+      <xdr:rowOff>219075</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -623,8 +623,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1466850" y="3609975"/>
-          <a:ext cx="1600200" cy="450850"/>
+          <a:off x="180975" y="3552825"/>
+          <a:ext cx="1600200" cy="885825"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -644,13 +644,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>561975</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>711200</xdr:rowOff>
+      <xdr:rowOff>795337</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1038225</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>882650</xdr:rowOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>80962</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -659,7 +659,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1228725" y="3657600"/>
+          <a:off x="1362075" y="4129087"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -693,33 +693,37 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>180976</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
+      <xdr:rowOff>219075</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="12" name="Back_12"/>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvPr id="12" name="Edge_12"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="4" idx="2"/>
+          <a:endCxn id="2" idx="0"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="333375" y="3390900"/>
-          <a:ext cx="514350" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
+        <a:xfrm flipV="1">
+          <a:off x="180975" y="1781175"/>
+          <a:ext cx="1" cy="1771650"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
           <a:avLst/>
         </a:prstGeom>
         <a:ln w="12700">
           <a:solidFill>
             <a:srgbClr val="333333"/>
           </a:solidFill>
+          <a:tailEnd type="triangle"/>
         </a:ln>
       </xdr:spPr>
     </xdr:cxnSp>
@@ -728,95 +732,24 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="13" name="Back_13"/>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="333375" y="1612900"/>
-          <a:ext cx="0" cy="1778000"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="14" name="Back_14"/>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="333375" y="1612900"/>
-          <a:ext cx="514350" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>358775</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>530225</xdr:rowOff>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>523875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="Label_15"/>
+        <xdr:cNvPr id="13" name="Label_13"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="476250" y="3305175"/>
+          <a:off x="561975" y="2800350"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -849,20 +782,20 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>981075</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
+      <xdr:colOff>981075</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
+      <xdr:rowOff>219075</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="16" name="Edge_16"/>
+        <xdr:cNvPr id="14" name="Edge_14"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="5" idx="2"/>
           <a:endCxn id="6" idx="0"/>
@@ -870,8 +803,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3067050" y="4498975"/>
-          <a:ext cx="1600200" cy="450850"/>
+          <a:off x="1781175" y="4438650"/>
+          <a:ext cx="1600200" cy="885825"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -888,20 +821,20 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>981075</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>800101</xdr:colOff>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>981076</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
+      <xdr:rowOff>219075</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="17" name="Edge_17"/>
+        <xdr:cNvPr id="15" name="Edge_15"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="6" idx="2"/>
           <a:endCxn id="7" idx="0"/>
@@ -909,8 +842,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4667250" y="5387975"/>
-          <a:ext cx="1" cy="450850"/>
+          <a:off x="3381375" y="5324475"/>
+          <a:ext cx="1" cy="885825"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -1217,10 +1150,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
@@ -1240,57 +1173,57 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="3" t="inlineStr">
+    <row r="3" ht="63" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>営業部</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>倉庫</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>経理部</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="4" t="n"/>
+    <row r="4" ht="69.75" customHeight="1">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="4" t="n"/>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="4" t="n"/>
+    <row r="5" ht="69.75" customHeight="1">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="4" t="n"/>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="4" t="n"/>
+    <row r="6" ht="69.75" customHeight="1">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="4" t="n"/>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="4" t="n"/>
+    <row r="7" ht="69.75" customHeight="1">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="4" t="n"/>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="4" t="n"/>
+    <row r="8" ht="69.75" customHeight="1">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="4" t="n"/>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="4" t="n"/>
+    <row r="9" ht="69.75" customHeight="1">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>

--- a/examples/sales_to_billing.xlsx
+++ b/examples/sales_to_billing.xlsx
@@ -10,7 +10,9 @@
     <sheet name="フロー図" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="注記" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'フロー図'!$A$1:$D$9</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -206,14 +208,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>180975</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>619125</xdr:colOff>
+      <xdr:colOff>1419225</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>657225</xdr:rowOff>
     </xdr:to>
@@ -224,7 +226,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="180975" y="1781175"/>
+          <a:off x="981075" y="1781175"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartTerminator">
@@ -259,14 +261,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>180975</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>619125</xdr:colOff>
+      <xdr:colOff>1419225</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>657225</xdr:rowOff>
     </xdr:to>
@@ -277,7 +279,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="180975" y="2667000"/>
+          <a:off x="981075" y="2667000"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -312,14 +314,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>180975</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>619125</xdr:colOff>
+      <xdr:colOff>1419225</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>657225</xdr:rowOff>
     </xdr:to>
@@ -330,7 +332,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="180975" y="3552825"/>
+          <a:off x="981075" y="3552825"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartDecision">
@@ -365,14 +367,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>981075</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>619125</xdr:colOff>
+      <xdr:colOff>1419225</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>657225</xdr:rowOff>
     </xdr:to>
@@ -383,7 +385,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1781175" y="4438650"/>
+          <a:off x="2581275" y="4438650"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -418,14 +420,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>981075</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>619125</xdr:colOff>
+      <xdr:colOff>1419225</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>657225</xdr:rowOff>
     </xdr:to>
@@ -436,7 +438,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3381375" y="5324475"/>
+          <a:off x="4181475" y="5324475"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -471,14 +473,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>981075</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>619125</xdr:colOff>
+      <xdr:colOff>1419225</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>657225</xdr:rowOff>
     </xdr:to>
@@ -489,7 +491,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3381375" y="6210300"/>
+          <a:off x="4181475" y="6210300"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartTerminator">
@@ -524,13 +526,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>180975</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>180976</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
@@ -545,7 +547,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="180975" y="1781175"/>
+          <a:off x="981075" y="1781175"/>
           <a:ext cx="1" cy="885825"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
@@ -563,13 +565,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>180975</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>180976</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
@@ -584,7 +586,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="180975" y="2667000"/>
+          <a:off x="981075" y="2667000"/>
           <a:ext cx="1" cy="885825"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
@@ -602,14 +604,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>180975</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>981075</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
     </xdr:to>
@@ -623,7 +625,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="180975" y="3552825"/>
+          <a:off x="981075" y="3552825"/>
           <a:ext cx="1600200" cy="885825"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
@@ -642,15 +644,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>561975</xdr:colOff>
+      <xdr:colOff>962025</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>795337</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1038225</xdr:colOff>
+      <xdr:rowOff>752475</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1438275</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>80962</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -659,7 +661,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1362075" y="4129087"/>
+          <a:off x="1762125" y="4086225"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -692,14 +694,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>-4219575</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>180976</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>800100</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
     </xdr:to>
@@ -707,14 +709,14 @@
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="12" name="Edge_12"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="4" idx="2"/>
-          <a:endCxn id="2" idx="0"/>
+          <a:stCxn id="4" idx="1"/>
+          <a:endCxn id="2" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="180975" y="1781175"/>
-          <a:ext cx="1" cy="1771650"/>
+          <a:off x="-219075" y="1781175"/>
+          <a:ext cx="1819275" cy="1771650"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -732,14 +734,14 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>561975</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>523875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -749,7 +751,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="561975" y="2800350"/>
+          <a:off x="409575" y="3686175"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -782,14 +784,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>981075</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>981075</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
     </xdr:to>
@@ -803,7 +805,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1781175" y="4438650"/>
+          <a:off x="2581275" y="4438650"/>
           <a:ext cx="1600200" cy="885825"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
@@ -821,14 +823,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>981075</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>981076</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>180976</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
     </xdr:to>
@@ -842,7 +844,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3381375" y="5324475"/>
+          <a:off x="4181475" y="5324475"/>
           <a:ext cx="1" cy="885825"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
@@ -1148,9 +1150,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1174,58 +1176,59 @@
       </c>
     </row>
     <row r="3" ht="63" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>営業部</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>倉庫</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>経理部</t>
         </is>
       </c>
     </row>
     <row r="4" ht="69.75" customHeight="1">
-      <c r="A4" s="4" t="n"/>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="4" t="n"/>
     </row>
     <row r="5" ht="69.75" customHeight="1">
-      <c r="A5" s="4" t="n"/>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="4" t="n"/>
     </row>
     <row r="6" ht="69.75" customHeight="1">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="4" t="n"/>
     </row>
     <row r="7" ht="69.75" customHeight="1">
-      <c r="A7" s="4" t="n"/>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="4" t="n"/>
     </row>
     <row r="8" ht="69.75" customHeight="1">
-      <c r="A8" s="4" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="4" t="n"/>
     </row>
     <row r="9" ht="69.75" customHeight="1">
-      <c r="A9" s="4" t="n"/>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>

--- a/examples/sales_to_billing.xlsx
+++ b/examples/sales_to_billing.xlsx
@@ -527,13 +527,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
+      <xdr:colOff>800100</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>180976</xdr:colOff>
+      <xdr:rowOff>657225</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>800101</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
     </xdr:to>
@@ -547,8 +547,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="981075" y="1781175"/>
-          <a:ext cx="1" cy="885825"/>
+          <a:off x="1600200" y="2219325"/>
+          <a:ext cx="1" cy="447675"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -566,13 +566,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
+      <xdr:colOff>800100</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>180976</xdr:colOff>
+      <xdr:rowOff>657225</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>800101</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
     </xdr:to>
@@ -586,8 +586,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="981075" y="2667000"/>
-          <a:ext cx="1" cy="885825"/>
+          <a:off x="1600200" y="3105150"/>
+          <a:ext cx="1" cy="447675"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -605,13 +605,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
+      <xdr:colOff>800100</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
+      <xdr:rowOff>657225</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
+      <xdr:colOff>800100</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
     </xdr:to>
@@ -625,8 +625,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="981075" y="3552825"/>
-          <a:ext cx="1600200" cy="885825"/>
+          <a:off x="1600200" y="3990975"/>
+          <a:ext cx="1600200" cy="447675"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -694,31 +694,98 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>-4219575</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
+      <xdr:rowOff>438150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>438150</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="12" name="Edge_12"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="4" idx="1"/>
-          <a:endCxn id="2" idx="1"/>
-        </xdr:cNvCxnSpPr>
+        <xdr:cNvPr id="12" name="Back_12"/>
+        <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="-219075" y="1781175"/>
-          <a:ext cx="1819275" cy="1771650"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
+        <a:xfrm>
+          <a:off x="400050" y="3771900"/>
+          <a:ext cx="581025" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>438150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>438150</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="13" name="Back_13"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="400050" y="2000250"/>
+          <a:ext cx="0" cy="1771650"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>438150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>438150</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="14" name="Back_14"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="400050" y="2000250"/>
+          <a:ext cx="581025" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
           <a:avLst/>
         </a:prstGeom>
         <a:ln w="12700">
@@ -746,7 +813,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="Label_13"/>
+        <xdr:cNvPr id="15" name="Label_15"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -785,19 +852,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
+      <xdr:colOff>800100</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
+      <xdr:rowOff>657225</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
+      <xdr:colOff>800100</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="14" name="Edge_14"/>
+        <xdr:cNvPr id="16" name="Edge_16"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="5" idx="2"/>
           <a:endCxn id="6" idx="0"/>
@@ -805,8 +872,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2581275" y="4438650"/>
-          <a:ext cx="1600200" cy="885825"/>
+          <a:off x="3200400" y="4876800"/>
+          <a:ext cx="1600200" cy="447675"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -824,19 +891,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
+      <xdr:colOff>800100</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
+      <xdr:rowOff>657225</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>180976</xdr:colOff>
+      <xdr:colOff>800101</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="15" name="Edge_15"/>
+        <xdr:cNvPr id="17" name="Edge_17"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="6" idx="2"/>
           <a:endCxn id="7" idx="0"/>
@@ -844,8 +911,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4181475" y="5324475"/>
-          <a:ext cx="1" cy="885825"/>
+          <a:off x="4800600" y="5762625"/>
+          <a:ext cx="1" cy="447675"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>

--- a/examples/sales_to_billing.xlsx
+++ b/examples/sales_to_billing.xlsx
@@ -696,7 +696,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>400050</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>438150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
@@ -708,86 +708,39 @@
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="12" name="Back_12"/>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="4" idx="1"/>
+          <a:endCxn id="2" idx="1"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="400050" y="3771900"/>
-          <a:ext cx="581025" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>400050</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>438150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>400050</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>438150</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="13" name="Back_13"/>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
           <a:off x="400050" y="2000250"/>
-          <a:ext cx="0" cy="1771650"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>400050</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>438150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>438150</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="14" name="Back_14"/>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="400050" y="2000250"/>
-          <a:ext cx="581025" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
+          <a:ext cx="581025" cy="1771650"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="100000" y="100000"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="0" y="100000"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="100000" y="0"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
         <a:ln w="12700">
           <a:solidFill>
             <a:srgbClr val="333333"/>
@@ -813,7 +766,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="Label_15"/>
+        <xdr:cNvPr id="13" name="Label_13"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -864,7 +817,7 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="16" name="Edge_16"/>
+        <xdr:cNvPr id="14" name="Edge_14"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="5" idx="2"/>
           <a:endCxn id="6" idx="0"/>
@@ -903,7 +856,7 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="17" name="Edge_17"/>
+        <xdr:cNvPr id="15" name="Edge_15"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="6" idx="2"/>
           <a:endCxn id="7" idx="0"/>

--- a/examples/sales_to_billing.xlsx
+++ b/examples/sales_to_billing.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="フロー図" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="注記" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="フロー図" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="注記" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'フロー図'!$A$1:$D$9</definedName>
@@ -209,6 +209,324 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
+      <xdr:colOff>742950</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>600075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>857250</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>276225</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Edge_8"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1543050" y="2162175"/>
+          <a:ext cx="114300" cy="561975"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="50000" y="10169"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="50000" y="89830"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>742950</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>600075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>857250</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>276225</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Edge_9"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1543050" y="3048000"/>
+          <a:ext cx="114300" cy="561975"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="50000" y="10169"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="50000" y="89830"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>742950</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>600075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>857250</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>276225</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Edge_10"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1543050" y="3933825"/>
+          <a:ext cx="1714500" cy="561975"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="3333" y="10169"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="3333" y="49999"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="96666" y="49999"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="96666" y="89830"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>742950</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>381000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>276225</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Edge_12"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1543050" y="1943100"/>
+          <a:ext cx="904875" cy="1666875"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="6315" y="96571"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="93684" y="96571"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="93684" y="3428"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="74736" y="3428"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>742950</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>600075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>857250</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>276225</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="Edge_14"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3143250" y="4819650"/>
+          <a:ext cx="1714500" cy="561975"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="3333" y="10169"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="3333" y="49999"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="96666" y="49999"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="96666" y="89830"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>742950</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>600075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>857250</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>276225</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="Edge_15"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4743450" y="5705475"/>
+          <a:ext cx="114300" cy="561975"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="50000" y="10169"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="50000" y="89830"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>180975</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
@@ -526,131 +844,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>657225</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>800101</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="8" name="Edge_8"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="2" idx="2"/>
-          <a:endCxn id="3" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1600200" y="2219325"/>
-          <a:ext cx="1" cy="447675"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>657225</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>800101</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="9" name="Edge_9"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="3" idx="2"/>
-          <a:endCxn id="4" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1600200" y="3105150"/>
-          <a:ext cx="1" cy="447675"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>657225</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="10" name="Edge_10"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="4" idx="2"/>
-          <a:endCxn id="5" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1600200" y="3990975"/>
-          <a:ext cx="1600200" cy="447675"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>962025</xdr:colOff>
+      <xdr:colOff>161925</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>752475</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1438275</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>638175</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
@@ -661,7 +862,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1762125" y="4086225"/>
+          <a:off x="2562225" y="4086225"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -690,65 +891,6 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>400050</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>438150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>438150</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="12" name="Back_12"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="4" idx="1"/>
-          <a:endCxn id="2" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="400050" y="2000250"/>
-          <a:ext cx="581025" cy="1771650"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst/>
-          <a:ahLst/>
-          <a:cxnLst/>
-          <a:rect l="0" t="0" r="100000" b="100000"/>
-          <a:pathLst>
-            <a:path w="100000" h="100000">
-              <a:moveTo>
-                <a:pt x="100000" y="100000"/>
-              </a:moveTo>
-              <a:lnTo>
-                <a:pt x="0" y="100000"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="0" y="0"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="100000" y="0"/>
-              </a:lnTo>
-            </a:path>
-          </a:pathLst>
-        </a:custGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
@@ -800,84 +942,6 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>657225</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="14" name="Edge_14"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="5" idx="2"/>
-          <a:endCxn id="6" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3200400" y="4876800"/>
-          <a:ext cx="1600200" cy="447675"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>657225</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>800101</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="15" name="Edge_15"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="6" idx="2"/>
-          <a:endCxn id="7" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4800600" y="5762625"/>
-          <a:ext cx="1" cy="447675"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
